--- a/PEI_requirements.xlsx
+++ b/PEI_requirements.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -19489,7 +19489,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -19504,23 +19504,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -19534,12 +19518,27 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="26">
+  <dxfs count="20">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -19557,106 +19556,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -19777,6 +19676,46 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -23036,7 +22975,7 @@
       <c r="B2" s="3" t="s">
         <v>1715</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="15" t="s">
         <v>1685</v>
       </c>
     </row>
@@ -23047,7 +22986,7 @@
       <c r="B3" s="3" t="s">
         <v>1714</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="C3" s="15" t="s">
         <v>1686</v>
       </c>
     </row>
@@ -23058,7 +22997,7 @@
       <c r="B4" s="3" t="s">
         <v>1716</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="15" t="s">
         <v>1687</v>
       </c>
     </row>
@@ -23069,7 +23008,7 @@
       <c r="B5" s="3" t="s">
         <v>1717</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="15" t="s">
         <v>1688</v>
       </c>
     </row>
@@ -23080,7 +23019,7 @@
       <c r="B6" s="3" t="s">
         <v>1718</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="15" t="s">
         <v>1689</v>
       </c>
     </row>
@@ -23091,7 +23030,7 @@
       <c r="B7" s="3" t="s">
         <v>1719</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="C7" s="15" t="s">
         <v>1690</v>
       </c>
     </row>
@@ -23102,7 +23041,7 @@
       <c r="B8" s="3" t="s">
         <v>1720</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="15" t="s">
         <v>1691</v>
       </c>
     </row>
@@ -23113,7 +23052,7 @@
       <c r="B9" s="3" t="s">
         <v>1721</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="C9" s="15" t="s">
         <v>1692</v>
       </c>
     </row>
@@ -23124,7 +23063,7 @@
       <c r="B10" s="3" t="s">
         <v>1722</v>
       </c>
-      <c r="C10" s="21" t="s">
+      <c r="C10" s="15" t="s">
         <v>1693</v>
       </c>
     </row>
@@ -23135,7 +23074,7 @@
       <c r="B11" s="3" t="s">
         <v>1723</v>
       </c>
-      <c r="C11" s="21" t="s">
+      <c r="C11" s="15" t="s">
         <v>1694</v>
       </c>
     </row>
@@ -23146,7 +23085,7 @@
       <c r="B12" s="3" t="s">
         <v>1724</v>
       </c>
-      <c r="C12" s="21" t="s">
+      <c r="C12" s="15" t="s">
         <v>1695</v>
       </c>
     </row>
@@ -23157,7 +23096,7 @@
       <c r="B13" s="3" t="s">
         <v>1725</v>
       </c>
-      <c r="C13" s="21" t="s">
+      <c r="C13" s="15" t="s">
         <v>1696</v>
       </c>
     </row>
@@ -23168,7 +23107,7 @@
       <c r="B14" s="3" t="s">
         <v>1726</v>
       </c>
-      <c r="C14" s="21" t="s">
+      <c r="C14" s="15" t="s">
         <v>1697</v>
       </c>
     </row>
@@ -23179,7 +23118,7 @@
       <c r="B15" s="3" t="s">
         <v>1727</v>
       </c>
-      <c r="C15" s="21" t="s">
+      <c r="C15" s="15" t="s">
         <v>1698</v>
       </c>
     </row>
@@ -23220,14 +23159,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="16" t="s">
         <v>1503</v>
       </c>
-      <c r="B1" s="13"/>
+      <c r="B1" s="16"/>
     </row>
     <row r="2" spans="1:8" s="1" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="13"/>
-      <c r="B2" s="13"/>
+      <c r="A2" s="16"/>
+      <c r="B2" s="16"/>
     </row>
     <row r="3" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
@@ -23925,111 +23864,111 @@
     <row r="106" spans="3:15" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="107" spans="3:15" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="108" spans="3:15" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C108" s="10" t="s">
+      <c r="C108" s="18" t="s">
         <v>1456</v>
       </c>
-      <c r="D108" s="10"/>
-      <c r="E108" s="10"/>
-      <c r="F108" s="10"/>
-      <c r="G108" s="10"/>
-      <c r="H108" s="10"/>
-      <c r="I108" s="10"/>
-      <c r="J108" s="10"/>
-      <c r="K108" s="10"/>
-      <c r="L108" s="10"/>
-      <c r="M108" s="10"/>
-      <c r="N108" s="10"/>
-      <c r="O108" s="10"/>
+      <c r="D108" s="18"/>
+      <c r="E108" s="18"/>
+      <c r="F108" s="18"/>
+      <c r="G108" s="18"/>
+      <c r="H108" s="18"/>
+      <c r="I108" s="18"/>
+      <c r="J108" s="18"/>
+      <c r="K108" s="18"/>
+      <c r="L108" s="18"/>
+      <c r="M108" s="18"/>
+      <c r="N108" s="18"/>
+      <c r="O108" s="18"/>
     </row>
     <row r="109" spans="3:15" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C109" s="10"/>
-      <c r="D109" s="10"/>
-      <c r="E109" s="10"/>
-      <c r="F109" s="10"/>
-      <c r="G109" s="10"/>
-      <c r="H109" s="10"/>
-      <c r="I109" s="10"/>
-      <c r="J109" s="10"/>
-      <c r="K109" s="10"/>
-      <c r="L109" s="10"/>
-      <c r="M109" s="10"/>
-      <c r="N109" s="10"/>
-      <c r="O109" s="10"/>
+      <c r="C109" s="18"/>
+      <c r="D109" s="18"/>
+      <c r="E109" s="18"/>
+      <c r="F109" s="18"/>
+      <c r="G109" s="18"/>
+      <c r="H109" s="18"/>
+      <c r="I109" s="18"/>
+      <c r="J109" s="18"/>
+      <c r="K109" s="18"/>
+      <c r="L109" s="18"/>
+      <c r="M109" s="18"/>
+      <c r="N109" s="18"/>
+      <c r="O109" s="18"/>
     </row>
     <row r="110" spans="3:15" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C110" s="10"/>
-      <c r="D110" s="10"/>
-      <c r="E110" s="10"/>
-      <c r="F110" s="10"/>
-      <c r="G110" s="10"/>
-      <c r="H110" s="10"/>
-      <c r="I110" s="10"/>
-      <c r="J110" s="10"/>
-      <c r="K110" s="10"/>
-      <c r="L110" s="10"/>
-      <c r="M110" s="10"/>
-      <c r="N110" s="10"/>
-      <c r="O110" s="10"/>
+      <c r="C110" s="18"/>
+      <c r="D110" s="18"/>
+      <c r="E110" s="18"/>
+      <c r="F110" s="18"/>
+      <c r="G110" s="18"/>
+      <c r="H110" s="18"/>
+      <c r="I110" s="18"/>
+      <c r="J110" s="18"/>
+      <c r="K110" s="18"/>
+      <c r="L110" s="18"/>
+      <c r="M110" s="18"/>
+      <c r="N110" s="18"/>
+      <c r="O110" s="18"/>
     </row>
     <row r="111" spans="3:15" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C111" s="10"/>
-      <c r="D111" s="10"/>
-      <c r="E111" s="10"/>
-      <c r="F111" s="10"/>
-      <c r="G111" s="10"/>
-      <c r="H111" s="10"/>
-      <c r="I111" s="10"/>
-      <c r="J111" s="10"/>
-      <c r="K111" s="10"/>
-      <c r="L111" s="10"/>
-      <c r="M111" s="10"/>
-      <c r="N111" s="10"/>
-      <c r="O111" s="10"/>
+      <c r="C111" s="18"/>
+      <c r="D111" s="18"/>
+      <c r="E111" s="18"/>
+      <c r="F111" s="18"/>
+      <c r="G111" s="18"/>
+      <c r="H111" s="18"/>
+      <c r="I111" s="18"/>
+      <c r="J111" s="18"/>
+      <c r="K111" s="18"/>
+      <c r="L111" s="18"/>
+      <c r="M111" s="18"/>
+      <c r="N111" s="18"/>
+      <c r="O111" s="18"/>
     </row>
     <row r="112" spans="3:15" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C112" s="10"/>
-      <c r="D112" s="10"/>
-      <c r="E112" s="10"/>
-      <c r="F112" s="10"/>
-      <c r="G112" s="10"/>
-      <c r="H112" s="10"/>
-      <c r="I112" s="10"/>
-      <c r="J112" s="10"/>
-      <c r="K112" s="10"/>
-      <c r="L112" s="10"/>
-      <c r="M112" s="10"/>
-      <c r="N112" s="10"/>
-      <c r="O112" s="10"/>
+      <c r="C112" s="18"/>
+      <c r="D112" s="18"/>
+      <c r="E112" s="18"/>
+      <c r="F112" s="18"/>
+      <c r="G112" s="18"/>
+      <c r="H112" s="18"/>
+      <c r="I112" s="18"/>
+      <c r="J112" s="18"/>
+      <c r="K112" s="18"/>
+      <c r="L112" s="18"/>
+      <c r="M112" s="18"/>
+      <c r="N112" s="18"/>
+      <c r="O112" s="18"/>
     </row>
     <row r="113" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C113" s="10"/>
-      <c r="D113" s="10"/>
-      <c r="E113" s="10"/>
-      <c r="F113" s="10"/>
-      <c r="G113" s="10"/>
-      <c r="H113" s="10"/>
-      <c r="I113" s="10"/>
-      <c r="J113" s="10"/>
-      <c r="K113" s="10"/>
-      <c r="L113" s="10"/>
-      <c r="M113" s="10"/>
-      <c r="N113" s="10"/>
-      <c r="O113" s="10"/>
+      <c r="C113" s="18"/>
+      <c r="D113" s="18"/>
+      <c r="E113" s="18"/>
+      <c r="F113" s="18"/>
+      <c r="G113" s="18"/>
+      <c r="H113" s="18"/>
+      <c r="I113" s="18"/>
+      <c r="J113" s="18"/>
+      <c r="K113" s="18"/>
+      <c r="L113" s="18"/>
+      <c r="M113" s="18"/>
+      <c r="N113" s="18"/>
+      <c r="O113" s="18"/>
     </row>
     <row r="114" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C114" s="10"/>
-      <c r="D114" s="10"/>
-      <c r="E114" s="10"/>
-      <c r="F114" s="10"/>
-      <c r="G114" s="10"/>
-      <c r="H114" s="10"/>
-      <c r="I114" s="10"/>
-      <c r="J114" s="10"/>
-      <c r="K114" s="10"/>
-      <c r="L114" s="10"/>
-      <c r="M114" s="10"/>
-      <c r="N114" s="10"/>
-      <c r="O114" s="10"/>
+      <c r="C114" s="18"/>
+      <c r="D114" s="18"/>
+      <c r="E114" s="18"/>
+      <c r="F114" s="18"/>
+      <c r="G114" s="18"/>
+      <c r="H114" s="18"/>
+      <c r="I114" s="18"/>
+      <c r="J114" s="18"/>
+      <c r="K114" s="18"/>
+      <c r="L114" s="18"/>
+      <c r="M114" s="18"/>
+      <c r="N114" s="18"/>
+      <c r="O114" s="18"/>
     </row>
     <row r="115" spans="1:15" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="116" spans="1:15" customFormat="1" x14ac:dyDescent="0.3"/>
@@ -24987,27 +24926,27 @@
       <c r="V550" s="1"/>
     </row>
     <row r="551" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="C551" s="11" t="s">
+      <c r="C551" s="19" t="s">
         <v>1498</v>
       </c>
-      <c r="D551" s="11"/>
-      <c r="E551" s="11"/>
-      <c r="F551" s="11"/>
-      <c r="G551" s="11"/>
-      <c r="K551" s="11" t="s">
+      <c r="D551" s="19"/>
+      <c r="E551" s="19"/>
+      <c r="F551" s="19"/>
+      <c r="G551" s="19"/>
+      <c r="K551" s="19" t="s">
         <v>1499</v>
       </c>
-      <c r="L551" s="11"/>
-      <c r="M551" s="11"/>
-      <c r="N551" s="11"/>
-      <c r="O551" s="11"/>
-      <c r="R551" s="11" t="s">
+      <c r="L551" s="19"/>
+      <c r="M551" s="19"/>
+      <c r="N551" s="19"/>
+      <c r="O551" s="19"/>
+      <c r="R551" s="19" t="s">
         <v>1500</v>
       </c>
-      <c r="S551" s="11"/>
-      <c r="T551" s="11"/>
-      <c r="U551" s="11"/>
-      <c r="V551" s="11"/>
+      <c r="S551" s="19"/>
+      <c r="T551" s="19"/>
+      <c r="U551" s="19"/>
+      <c r="V551" s="19"/>
     </row>
     <row r="552" spans="1:22" x14ac:dyDescent="0.3">
       <c r="R552" s="1"/>
@@ -38158,18 +38097,18 @@
     <mergeCell ref="K551:O551"/>
   </mergeCells>
   <conditionalFormatting sqref="Q159:Q163">
-    <cfRule type="containsText" dxfId="21" priority="3" operator="containsText" text="true">
+    <cfRule type="containsText" dxfId="17" priority="3" operator="containsText" text="true">
       <formula>NOT(ISERROR(SEARCH("true",Q159)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="20" priority="4" operator="containsText" text="false">
+    <cfRule type="containsText" dxfId="16" priority="4" operator="containsText" text="false">
       <formula>NOT(ISERROR(SEARCH("false",Q159)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R566:V815">
-    <cfRule type="containsText" dxfId="19" priority="1" operator="containsText" text="true">
+    <cfRule type="containsText" dxfId="15" priority="1" operator="containsText" text="true">
       <formula>NOT(ISERROR(SEARCH("true",R566)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="18" priority="2" operator="containsText" text="false">
+    <cfRule type="containsText" dxfId="14" priority="2" operator="containsText" text="false">
       <formula>NOT(ISERROR(SEARCH("false",R566)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -38613,10 +38552,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F1:F21 E22:E1048576">
-    <cfRule type="containsText" dxfId="17" priority="1" operator="containsText" text="FAIL">
+    <cfRule type="containsText" dxfId="13" priority="1" operator="containsText" text="FAIL">
       <formula>NOT(ISERROR(SEARCH("FAIL",E1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="16" priority="2" operator="containsText" text="PASS">
+    <cfRule type="containsText" dxfId="12" priority="2" operator="containsText" text="PASS">
       <formula>NOT(ISERROR(SEARCH("PASS",E1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -38640,14 +38579,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="16" t="s">
         <v>1504</v>
       </c>
-      <c r="B1" s="13"/>
+      <c r="B1" s="16"/>
     </row>
     <row r="2" spans="1:8" s="1" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="13"/>
-      <c r="B2" s="13"/>
+      <c r="A2" s="16"/>
+      <c r="B2" s="16"/>
     </row>
     <row r="3" spans="1:8" s="1" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:8" s="1" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -39350,111 +39289,111 @@
     <row r="106" spans="3:15" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="107" spans="3:15" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="108" spans="3:15" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C108" s="10" t="s">
+      <c r="C108" s="18" t="s">
         <v>1456</v>
       </c>
-      <c r="D108" s="10"/>
-      <c r="E108" s="10"/>
-      <c r="F108" s="10"/>
-      <c r="G108" s="10"/>
-      <c r="H108" s="10"/>
-      <c r="I108" s="10"/>
-      <c r="J108" s="10"/>
-      <c r="K108" s="10"/>
-      <c r="L108" s="10"/>
-      <c r="M108" s="10"/>
-      <c r="N108" s="10"/>
-      <c r="O108" s="10"/>
+      <c r="D108" s="18"/>
+      <c r="E108" s="18"/>
+      <c r="F108" s="18"/>
+      <c r="G108" s="18"/>
+      <c r="H108" s="18"/>
+      <c r="I108" s="18"/>
+      <c r="J108" s="18"/>
+      <c r="K108" s="18"/>
+      <c r="L108" s="18"/>
+      <c r="M108" s="18"/>
+      <c r="N108" s="18"/>
+      <c r="O108" s="18"/>
     </row>
     <row r="109" spans="3:15" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C109" s="10"/>
-      <c r="D109" s="10"/>
-      <c r="E109" s="10"/>
-      <c r="F109" s="10"/>
-      <c r="G109" s="10"/>
-      <c r="H109" s="10"/>
-      <c r="I109" s="10"/>
-      <c r="J109" s="10"/>
-      <c r="K109" s="10"/>
-      <c r="L109" s="10"/>
-      <c r="M109" s="10"/>
-      <c r="N109" s="10"/>
-      <c r="O109" s="10"/>
+      <c r="C109" s="18"/>
+      <c r="D109" s="18"/>
+      <c r="E109" s="18"/>
+      <c r="F109" s="18"/>
+      <c r="G109" s="18"/>
+      <c r="H109" s="18"/>
+      <c r="I109" s="18"/>
+      <c r="J109" s="18"/>
+      <c r="K109" s="18"/>
+      <c r="L109" s="18"/>
+      <c r="M109" s="18"/>
+      <c r="N109" s="18"/>
+      <c r="O109" s="18"/>
     </row>
     <row r="110" spans="3:15" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C110" s="10"/>
-      <c r="D110" s="10"/>
-      <c r="E110" s="10"/>
-      <c r="F110" s="10"/>
-      <c r="G110" s="10"/>
-      <c r="H110" s="10"/>
-      <c r="I110" s="10"/>
-      <c r="J110" s="10"/>
-      <c r="K110" s="10"/>
-      <c r="L110" s="10"/>
-      <c r="M110" s="10"/>
-      <c r="N110" s="10"/>
-      <c r="O110" s="10"/>
+      <c r="C110" s="18"/>
+      <c r="D110" s="18"/>
+      <c r="E110" s="18"/>
+      <c r="F110" s="18"/>
+      <c r="G110" s="18"/>
+      <c r="H110" s="18"/>
+      <c r="I110" s="18"/>
+      <c r="J110" s="18"/>
+      <c r="K110" s="18"/>
+      <c r="L110" s="18"/>
+      <c r="M110" s="18"/>
+      <c r="N110" s="18"/>
+      <c r="O110" s="18"/>
     </row>
     <row r="111" spans="3:15" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C111" s="10"/>
-      <c r="D111" s="10"/>
-      <c r="E111" s="10"/>
-      <c r="F111" s="10"/>
-      <c r="G111" s="10"/>
-      <c r="H111" s="10"/>
-      <c r="I111" s="10"/>
-      <c r="J111" s="10"/>
-      <c r="K111" s="10"/>
-      <c r="L111" s="10"/>
-      <c r="M111" s="10"/>
-      <c r="N111" s="10"/>
-      <c r="O111" s="10"/>
+      <c r="C111" s="18"/>
+      <c r="D111" s="18"/>
+      <c r="E111" s="18"/>
+      <c r="F111" s="18"/>
+      <c r="G111" s="18"/>
+      <c r="H111" s="18"/>
+      <c r="I111" s="18"/>
+      <c r="J111" s="18"/>
+      <c r="K111" s="18"/>
+      <c r="L111" s="18"/>
+      <c r="M111" s="18"/>
+      <c r="N111" s="18"/>
+      <c r="O111" s="18"/>
     </row>
     <row r="112" spans="3:15" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C112" s="10"/>
-      <c r="D112" s="10"/>
-      <c r="E112" s="10"/>
-      <c r="F112" s="10"/>
-      <c r="G112" s="10"/>
-      <c r="H112" s="10"/>
-      <c r="I112" s="10"/>
-      <c r="J112" s="10"/>
-      <c r="K112" s="10"/>
-      <c r="L112" s="10"/>
-      <c r="M112" s="10"/>
-      <c r="N112" s="10"/>
-      <c r="O112" s="10"/>
+      <c r="C112" s="18"/>
+      <c r="D112" s="18"/>
+      <c r="E112" s="18"/>
+      <c r="F112" s="18"/>
+      <c r="G112" s="18"/>
+      <c r="H112" s="18"/>
+      <c r="I112" s="18"/>
+      <c r="J112" s="18"/>
+      <c r="K112" s="18"/>
+      <c r="L112" s="18"/>
+      <c r="M112" s="18"/>
+      <c r="N112" s="18"/>
+      <c r="O112" s="18"/>
     </row>
     <row r="113" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C113" s="10"/>
-      <c r="D113" s="10"/>
-      <c r="E113" s="10"/>
-      <c r="F113" s="10"/>
-      <c r="G113" s="10"/>
-      <c r="H113" s="10"/>
-      <c r="I113" s="10"/>
-      <c r="J113" s="10"/>
-      <c r="K113" s="10"/>
-      <c r="L113" s="10"/>
-      <c r="M113" s="10"/>
-      <c r="N113" s="10"/>
-      <c r="O113" s="10"/>
+      <c r="C113" s="18"/>
+      <c r="D113" s="18"/>
+      <c r="E113" s="18"/>
+      <c r="F113" s="18"/>
+      <c r="G113" s="18"/>
+      <c r="H113" s="18"/>
+      <c r="I113" s="18"/>
+      <c r="J113" s="18"/>
+      <c r="K113" s="18"/>
+      <c r="L113" s="18"/>
+      <c r="M113" s="18"/>
+      <c r="N113" s="18"/>
+      <c r="O113" s="18"/>
     </row>
     <row r="114" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C114" s="10"/>
-      <c r="D114" s="10"/>
-      <c r="E114" s="10"/>
-      <c r="F114" s="10"/>
-      <c r="G114" s="10"/>
-      <c r="H114" s="10"/>
-      <c r="I114" s="10"/>
-      <c r="J114" s="10"/>
-      <c r="K114" s="10"/>
-      <c r="L114" s="10"/>
-      <c r="M114" s="10"/>
-      <c r="N114" s="10"/>
-      <c r="O114" s="10"/>
+      <c r="C114" s="18"/>
+      <c r="D114" s="18"/>
+      <c r="E114" s="18"/>
+      <c r="F114" s="18"/>
+      <c r="G114" s="18"/>
+      <c r="H114" s="18"/>
+      <c r="I114" s="18"/>
+      <c r="J114" s="18"/>
+      <c r="K114" s="18"/>
+      <c r="L114" s="18"/>
+      <c r="M114" s="18"/>
+      <c r="N114" s="18"/>
+      <c r="O114" s="18"/>
     </row>
     <row r="115" spans="1:15" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="116" spans="1:15" customFormat="1" x14ac:dyDescent="0.3"/>
@@ -39514,10 +39453,10 @@
     <row r="152" spans="3:23" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="153" spans="3:23" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="154" spans="3:23" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C154" s="14" t="s">
+      <c r="C154" s="10" t="s">
         <v>1457</v>
       </c>
-      <c r="M154" s="14" t="s">
+      <c r="M154" s="10" t="s">
         <v>1458</v>
       </c>
     </row>
@@ -40458,27 +40397,27 @@
       <c r="V508" s="1"/>
     </row>
     <row r="509" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="C509" s="11" t="s">
+      <c r="C509" s="19" t="s">
         <v>1498</v>
       </c>
-      <c r="D509" s="11"/>
-      <c r="E509" s="11"/>
-      <c r="F509" s="11"/>
-      <c r="G509" s="11"/>
-      <c r="K509" s="11" t="s">
+      <c r="D509" s="19"/>
+      <c r="E509" s="19"/>
+      <c r="F509" s="19"/>
+      <c r="G509" s="19"/>
+      <c r="K509" s="19" t="s">
         <v>1499</v>
       </c>
-      <c r="L509" s="11"/>
-      <c r="M509" s="11"/>
-      <c r="N509" s="11"/>
-      <c r="O509" s="11"/>
-      <c r="R509" s="11" t="s">
+      <c r="L509" s="19"/>
+      <c r="M509" s="19"/>
+      <c r="N509" s="19"/>
+      <c r="O509" s="19"/>
+      <c r="R509" s="19" t="s">
         <v>1500</v>
       </c>
-      <c r="S509" s="11"/>
-      <c r="T509" s="11"/>
-      <c r="U509" s="11"/>
-      <c r="V509" s="11"/>
+      <c r="S509" s="19"/>
+      <c r="T509" s="19"/>
+      <c r="U509" s="19"/>
+      <c r="V509" s="19"/>
     </row>
     <row r="510" spans="1:22" x14ac:dyDescent="0.3">
       <c r="R510" s="1"/>
@@ -40568,7 +40507,7 @@
         <v>250</v>
       </c>
       <c r="Y522">
-        <f t="shared" ref="Y522:AB522" si="1">COUNTIF(S524:S773,TRUE)</f>
+        <f t="shared" ref="Y522:AA522" si="1">COUNTIF(S524:S773,TRUE)</f>
         <v>250</v>
       </c>
       <c r="Z522">
@@ -40611,7 +40550,7 @@
         <v>1</v>
       </c>
       <c r="S523" t="b">
-        <f t="shared" ref="S523:V523" si="2">D523=L523</f>
+        <f t="shared" ref="S523:U523" si="2">D523=L523</f>
         <v>1</v>
       </c>
       <c r="T523" t="b">
@@ -40653,7 +40592,7 @@
         <v>1</v>
       </c>
       <c r="S524" t="b">
-        <f t="shared" ref="S524:V539" si="3">EXACT(D524,L524)</f>
+        <f t="shared" ref="S524:U539" si="3">EXACT(D524,L524)</f>
         <v>1</v>
       </c>
       <c r="T524" t="b">
@@ -40691,7 +40630,7 @@
         <v>262</v>
       </c>
       <c r="R525" t="b">
-        <f t="shared" ref="R525:V587" si="4">EXACT(C525,K525)</f>
+        <f t="shared" ref="R525:U587" si="4">EXACT(C525,K525)</f>
         <v>1</v>
       </c>
       <c r="S525" t="b">
@@ -40838,15 +40777,15 @@
       <c r="Z528" s="1" t="s">
         <v>1326</v>
       </c>
-      <c r="AB528" s="15" t="s">
+      <c r="AB528" s="20" t="s">
         <v>1561</v>
       </c>
-      <c r="AC528" s="15"/>
-      <c r="AD528" s="15"/>
-      <c r="AE528" s="15"/>
-      <c r="AF528" s="15"/>
-      <c r="AG528" s="15"/>
-      <c r="AH528" s="15"/>
+      <c r="AC528" s="20"/>
+      <c r="AD528" s="20"/>
+      <c r="AE528" s="20"/>
+      <c r="AF528" s="20"/>
+      <c r="AG528" s="20"/>
+      <c r="AH528" s="20"/>
     </row>
     <row r="529" spans="3:34" x14ac:dyDescent="0.3">
       <c r="C529" s="1" t="s">
@@ -40895,13 +40834,13 @@
       <c r="Z529" s="1" t="s">
         <v>1552</v>
       </c>
-      <c r="AB529" s="15"/>
-      <c r="AC529" s="15"/>
-      <c r="AD529" s="15"/>
-      <c r="AE529" s="15"/>
-      <c r="AF529" s="15"/>
-      <c r="AG529" s="15"/>
-      <c r="AH529" s="15"/>
+      <c r="AB529" s="20"/>
+      <c r="AC529" s="20"/>
+      <c r="AD529" s="20"/>
+      <c r="AE529" s="20"/>
+      <c r="AF529" s="20"/>
+      <c r="AG529" s="20"/>
+      <c r="AH529" s="20"/>
     </row>
     <row r="530" spans="3:34" x14ac:dyDescent="0.3">
       <c r="C530" s="1" t="s">
@@ -40950,13 +40889,13 @@
       <c r="Z530" s="1" t="s">
         <v>1553</v>
       </c>
-      <c r="AB530" s="15"/>
-      <c r="AC530" s="15"/>
-      <c r="AD530" s="15"/>
-      <c r="AE530" s="15"/>
-      <c r="AF530" s="15"/>
-      <c r="AG530" s="15"/>
-      <c r="AH530" s="15"/>
+      <c r="AB530" s="20"/>
+      <c r="AC530" s="20"/>
+      <c r="AD530" s="20"/>
+      <c r="AE530" s="20"/>
+      <c r="AF530" s="20"/>
+      <c r="AG530" s="20"/>
+      <c r="AH530" s="20"/>
     </row>
     <row r="531" spans="3:34" x14ac:dyDescent="0.3">
       <c r="C531" s="1" t="s">
@@ -41005,13 +40944,13 @@
       <c r="Z531" s="1" t="s">
         <v>1554</v>
       </c>
-      <c r="AB531" s="15"/>
-      <c r="AC531" s="15"/>
-      <c r="AD531" s="15"/>
-      <c r="AE531" s="15"/>
-      <c r="AF531" s="15"/>
-      <c r="AG531" s="15"/>
-      <c r="AH531" s="15"/>
+      <c r="AB531" s="20"/>
+      <c r="AC531" s="20"/>
+      <c r="AD531" s="20"/>
+      <c r="AE531" s="20"/>
+      <c r="AF531" s="20"/>
+      <c r="AG531" s="20"/>
+      <c r="AH531" s="20"/>
     </row>
     <row r="532" spans="3:34" x14ac:dyDescent="0.3">
       <c r="C532" s="1" t="s">
@@ -43391,7 +43330,7 @@
         <v>385</v>
       </c>
       <c r="R588" t="b">
-        <f t="shared" ref="R588:V638" si="5">EXACT(C588,K588)</f>
+        <f t="shared" ref="R588:U638" si="5">EXACT(C588,K588)</f>
         <v>1</v>
       </c>
       <c r="S588" t="b">
@@ -45533,7 +45472,7 @@
         <v>399</v>
       </c>
       <c r="R639" t="b">
-        <f t="shared" ref="R639:V689" si="6">EXACT(C639,K639)</f>
+        <f t="shared" ref="R639:U689" si="6">EXACT(C639,K639)</f>
         <v>1</v>
       </c>
       <c r="S639" t="b">
@@ -47675,7 +47614,7 @@
         <v>440</v>
       </c>
       <c r="R690" t="b">
-        <f t="shared" ref="R690:V740" si="7">EXACT(C690,K690)</f>
+        <f t="shared" ref="R690:U740" si="7">EXACT(C690,K690)</f>
         <v>1</v>
       </c>
       <c r="S690" t="b">
@@ -49817,7 +49756,7 @@
         <v>396</v>
       </c>
       <c r="R741" t="b">
-        <f t="shared" ref="R741:V773" si="8">EXACT(C741,K741)</f>
+        <f t="shared" ref="R741:U773" si="8">EXACT(C741,K741)</f>
         <v>1</v>
       </c>
       <c r="S741" t="b">
@@ -51191,26 +51130,18 @@
     <mergeCell ref="AB528:AH531"/>
   </mergeCells>
   <conditionalFormatting sqref="Q159:Q163">
-    <cfRule type="containsText" dxfId="15" priority="5" operator="containsText" text="true">
+    <cfRule type="containsText" dxfId="11" priority="5" operator="containsText" text="true">
       <formula>NOT(ISERROR(SEARCH("true",Q159)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="14" priority="6" operator="containsText" text="false">
+    <cfRule type="containsText" dxfId="10" priority="6" operator="containsText" text="false">
       <formula>NOT(ISERROR(SEARCH("false",Q159)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R524:V773">
-    <cfRule type="containsText" dxfId="13" priority="3" operator="containsText" text="true">
-      <formula>NOT(ISERROR(SEARCH("true",R524)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="4" operator="containsText" text="false">
-      <formula>NOT(ISERROR(SEARCH("false",R524)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R523:V523">
-    <cfRule type="containsText" dxfId="11" priority="1" operator="containsText" text="true">
+  <conditionalFormatting sqref="R523:V773">
+    <cfRule type="containsText" dxfId="9" priority="1" operator="containsText" text="true">
       <formula>NOT(ISERROR(SEARCH("true",R523)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="2" operator="containsText" text="false">
+    <cfRule type="containsText" dxfId="8" priority="2" operator="containsText" text="false">
       <formula>NOT(ISERROR(SEARCH("false",R523)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -51653,10 +51584,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F1:F21">
-    <cfRule type="containsText" dxfId="9" priority="1" operator="containsText" text="FAIL">
+    <cfRule type="containsText" dxfId="7" priority="1" operator="containsText" text="FAIL">
       <formula>NOT(ISERROR(SEARCH("FAIL",F1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="2" operator="containsText" text="PASS">
+    <cfRule type="containsText" dxfId="6" priority="2" operator="containsText" text="PASS">
       <formula>NOT(ISERROR(SEARCH("PASS",F1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -51680,14 +51611,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="16" t="s">
         <v>1606</v>
       </c>
-      <c r="B1" s="13"/>
+      <c r="B1" s="16"/>
     </row>
     <row r="2" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="13"/>
-      <c r="B2" s="13"/>
+      <c r="A2" s="16"/>
+      <c r="B2" s="16"/>
     </row>
     <row r="3" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
@@ -52389,111 +52320,111 @@
     <row r="106" spans="3:15" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="107" spans="3:15" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="108" spans="3:15" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C108" s="10" t="s">
+      <c r="C108" s="18" t="s">
         <v>1456</v>
       </c>
-      <c r="D108" s="10"/>
-      <c r="E108" s="10"/>
-      <c r="F108" s="10"/>
-      <c r="G108" s="10"/>
-      <c r="H108" s="10"/>
-      <c r="I108" s="10"/>
-      <c r="J108" s="10"/>
-      <c r="K108" s="10"/>
-      <c r="L108" s="10"/>
-      <c r="M108" s="10"/>
-      <c r="N108" s="10"/>
-      <c r="O108" s="10"/>
+      <c r="D108" s="18"/>
+      <c r="E108" s="18"/>
+      <c r="F108" s="18"/>
+      <c r="G108" s="18"/>
+      <c r="H108" s="18"/>
+      <c r="I108" s="18"/>
+      <c r="J108" s="18"/>
+      <c r="K108" s="18"/>
+      <c r="L108" s="18"/>
+      <c r="M108" s="18"/>
+      <c r="N108" s="18"/>
+      <c r="O108" s="18"/>
     </row>
     <row r="109" spans="3:15" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C109" s="10"/>
-      <c r="D109" s="10"/>
-      <c r="E109" s="10"/>
-      <c r="F109" s="10"/>
-      <c r="G109" s="10"/>
-      <c r="H109" s="10"/>
-      <c r="I109" s="10"/>
-      <c r="J109" s="10"/>
-      <c r="K109" s="10"/>
-      <c r="L109" s="10"/>
-      <c r="M109" s="10"/>
-      <c r="N109" s="10"/>
-      <c r="O109" s="10"/>
+      <c r="C109" s="18"/>
+      <c r="D109" s="18"/>
+      <c r="E109" s="18"/>
+      <c r="F109" s="18"/>
+      <c r="G109" s="18"/>
+      <c r="H109" s="18"/>
+      <c r="I109" s="18"/>
+      <c r="J109" s="18"/>
+      <c r="K109" s="18"/>
+      <c r="L109" s="18"/>
+      <c r="M109" s="18"/>
+      <c r="N109" s="18"/>
+      <c r="O109" s="18"/>
     </row>
     <row r="110" spans="3:15" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C110" s="10"/>
-      <c r="D110" s="10"/>
-      <c r="E110" s="10"/>
-      <c r="F110" s="10"/>
-      <c r="G110" s="10"/>
-      <c r="H110" s="10"/>
-      <c r="I110" s="10"/>
-      <c r="J110" s="10"/>
-      <c r="K110" s="10"/>
-      <c r="L110" s="10"/>
-      <c r="M110" s="10"/>
-      <c r="N110" s="10"/>
-      <c r="O110" s="10"/>
+      <c r="C110" s="18"/>
+      <c r="D110" s="18"/>
+      <c r="E110" s="18"/>
+      <c r="F110" s="18"/>
+      <c r="G110" s="18"/>
+      <c r="H110" s="18"/>
+      <c r="I110" s="18"/>
+      <c r="J110" s="18"/>
+      <c r="K110" s="18"/>
+      <c r="L110" s="18"/>
+      <c r="M110" s="18"/>
+      <c r="N110" s="18"/>
+      <c r="O110" s="18"/>
     </row>
     <row r="111" spans="3:15" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C111" s="10"/>
-      <c r="D111" s="10"/>
-      <c r="E111" s="10"/>
-      <c r="F111" s="10"/>
-      <c r="G111" s="10"/>
-      <c r="H111" s="10"/>
-      <c r="I111" s="10"/>
-      <c r="J111" s="10"/>
-      <c r="K111" s="10"/>
-      <c r="L111" s="10"/>
-      <c r="M111" s="10"/>
-      <c r="N111" s="10"/>
-      <c r="O111" s="10"/>
+      <c r="C111" s="18"/>
+      <c r="D111" s="18"/>
+      <c r="E111" s="18"/>
+      <c r="F111" s="18"/>
+      <c r="G111" s="18"/>
+      <c r="H111" s="18"/>
+      <c r="I111" s="18"/>
+      <c r="J111" s="18"/>
+      <c r="K111" s="18"/>
+      <c r="L111" s="18"/>
+      <c r="M111" s="18"/>
+      <c r="N111" s="18"/>
+      <c r="O111" s="18"/>
     </row>
     <row r="112" spans="3:15" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C112" s="10"/>
-      <c r="D112" s="10"/>
-      <c r="E112" s="10"/>
-      <c r="F112" s="10"/>
-      <c r="G112" s="10"/>
-      <c r="H112" s="10"/>
-      <c r="I112" s="10"/>
-      <c r="J112" s="10"/>
-      <c r="K112" s="10"/>
-      <c r="L112" s="10"/>
-      <c r="M112" s="10"/>
-      <c r="N112" s="10"/>
-      <c r="O112" s="10"/>
+      <c r="C112" s="18"/>
+      <c r="D112" s="18"/>
+      <c r="E112" s="18"/>
+      <c r="F112" s="18"/>
+      <c r="G112" s="18"/>
+      <c r="H112" s="18"/>
+      <c r="I112" s="18"/>
+      <c r="J112" s="18"/>
+      <c r="K112" s="18"/>
+      <c r="L112" s="18"/>
+      <c r="M112" s="18"/>
+      <c r="N112" s="18"/>
+      <c r="O112" s="18"/>
     </row>
     <row r="113" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C113" s="10"/>
-      <c r="D113" s="10"/>
-      <c r="E113" s="10"/>
-      <c r="F113" s="10"/>
-      <c r="G113" s="10"/>
-      <c r="H113" s="10"/>
-      <c r="I113" s="10"/>
-      <c r="J113" s="10"/>
-      <c r="K113" s="10"/>
-      <c r="L113" s="10"/>
-      <c r="M113" s="10"/>
-      <c r="N113" s="10"/>
-      <c r="O113" s="10"/>
+      <c r="C113" s="18"/>
+      <c r="D113" s="18"/>
+      <c r="E113" s="18"/>
+      <c r="F113" s="18"/>
+      <c r="G113" s="18"/>
+      <c r="H113" s="18"/>
+      <c r="I113" s="18"/>
+      <c r="J113" s="18"/>
+      <c r="K113" s="18"/>
+      <c r="L113" s="18"/>
+      <c r="M113" s="18"/>
+      <c r="N113" s="18"/>
+      <c r="O113" s="18"/>
     </row>
     <row r="114" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C114" s="10"/>
-      <c r="D114" s="10"/>
-      <c r="E114" s="10"/>
-      <c r="F114" s="10"/>
-      <c r="G114" s="10"/>
-      <c r="H114" s="10"/>
-      <c r="I114" s="10"/>
-      <c r="J114" s="10"/>
-      <c r="K114" s="10"/>
-      <c r="L114" s="10"/>
-      <c r="M114" s="10"/>
-      <c r="N114" s="10"/>
-      <c r="O114" s="10"/>
+      <c r="C114" s="18"/>
+      <c r="D114" s="18"/>
+      <c r="E114" s="18"/>
+      <c r="F114" s="18"/>
+      <c r="G114" s="18"/>
+      <c r="H114" s="18"/>
+      <c r="I114" s="18"/>
+      <c r="J114" s="18"/>
+      <c r="K114" s="18"/>
+      <c r="L114" s="18"/>
+      <c r="M114" s="18"/>
+      <c r="N114" s="18"/>
+      <c r="O114" s="18"/>
     </row>
     <row r="115" spans="1:15" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="116" spans="1:15" customFormat="1" x14ac:dyDescent="0.3"/>
@@ -52553,10 +52484,10 @@
     <row r="152" spans="3:23" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="153" spans="3:23" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="154" spans="3:23" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C154" s="14" t="s">
+      <c r="C154" s="10" t="s">
         <v>1457</v>
       </c>
-      <c r="M154" s="14" t="s">
+      <c r="M154" s="10" t="s">
         <v>1458</v>
       </c>
     </row>
@@ -54016,27 +53947,27 @@
       <c r="V436" s="1"/>
     </row>
     <row r="437" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="C437" s="11" t="s">
+      <c r="C437" s="19" t="s">
         <v>1498</v>
       </c>
-      <c r="D437" s="11"/>
-      <c r="E437" s="11"/>
-      <c r="F437" s="11"/>
-      <c r="G437" s="11"/>
-      <c r="K437" s="11" t="s">
+      <c r="D437" s="19"/>
+      <c r="E437" s="19"/>
+      <c r="F437" s="19"/>
+      <c r="G437" s="19"/>
+      <c r="K437" s="19" t="s">
         <v>1499</v>
       </c>
-      <c r="L437" s="11"/>
-      <c r="M437" s="11"/>
-      <c r="N437" s="11"/>
-      <c r="O437" s="11"/>
-      <c r="R437" s="11" t="s">
+      <c r="L437" s="19"/>
+      <c r="M437" s="19"/>
+      <c r="N437" s="19"/>
+      <c r="O437" s="19"/>
+      <c r="R437" s="19" t="s">
         <v>1500</v>
       </c>
-      <c r="S437" s="11"/>
-      <c r="T437" s="11"/>
-      <c r="U437" s="11"/>
-      <c r="V437" s="11"/>
+      <c r="S437" s="19"/>
+      <c r="T437" s="19"/>
+      <c r="U437" s="19"/>
+      <c r="V437" s="19"/>
     </row>
     <row r="438" spans="1:22" x14ac:dyDescent="0.3">
       <c r="R438" s="1"/>
@@ -54126,7 +54057,7 @@
         <v>250</v>
       </c>
       <c r="Y450">
-        <f t="shared" ref="Y450:AA450" si="1">COUNTIF(S452:S701,TRUE)</f>
+        <f t="shared" ref="Y450:Z450" si="1">COUNTIF(S452:S701,TRUE)</f>
         <v>250</v>
       </c>
       <c r="Z450">
@@ -54160,7 +54091,7 @@
         <v>1</v>
       </c>
       <c r="S451" t="b">
-        <f t="shared" ref="S451:U451" si="2">D451=L451</f>
+        <f t="shared" ref="S451:T451" si="2">D451=L451</f>
         <v>1</v>
       </c>
       <c r="T451" t="b">
@@ -54192,7 +54123,7 @@
         <v>1</v>
       </c>
       <c r="S452" t="b">
-        <f t="shared" ref="S452:U467" si="3">EXACT(D452,L452)</f>
+        <f t="shared" ref="S452:T467" si="3">EXACT(D452,L452)</f>
         <v>1</v>
       </c>
       <c r="T452" t="b">
@@ -54220,7 +54151,7 @@
         <v>472</v>
       </c>
       <c r="R453" t="b">
-        <f t="shared" ref="R453:U515" si="4">EXACT(C453,K453)</f>
+        <f t="shared" ref="R453:T515" si="4">EXACT(C453,K453)</f>
         <v>1</v>
       </c>
       <c r="S453" t="b">
@@ -56236,7 +56167,7 @@
         <v>298</v>
       </c>
       <c r="R516" t="b">
-        <f t="shared" ref="R516:U566" si="5">EXACT(C516,K516)</f>
+        <f t="shared" ref="R516:T566" si="5">EXACT(C516,K516)</f>
         <v>1</v>
       </c>
       <c r="S516" t="b">
@@ -57868,7 +57799,7 @@
         <v>297</v>
       </c>
       <c r="R567" t="b">
-        <f t="shared" ref="R567:U617" si="6">EXACT(C567,K567)</f>
+        <f t="shared" ref="R567:T617" si="6">EXACT(C567,K567)</f>
         <v>1</v>
       </c>
       <c r="S567" t="b">
@@ -59500,7 +59431,7 @@
         <v>490</v>
       </c>
       <c r="R618" t="b">
-        <f t="shared" ref="R618:U668" si="7">EXACT(C618,K618)</f>
+        <f t="shared" ref="R618:T668" si="7">EXACT(C618,K618)</f>
         <v>1</v>
       </c>
       <c r="S618" t="b">
@@ -61132,7 +61063,7 @@
         <v>296</v>
       </c>
       <c r="R669" t="b">
-        <f t="shared" ref="R669:U701" si="8">EXACT(C669,K669)</f>
+        <f t="shared" ref="R669:T701" si="8">EXACT(C669,K669)</f>
         <v>1</v>
       </c>
       <c r="S669" t="b">
@@ -62181,22 +62112,14 @@
     <mergeCell ref="R437:V437"/>
   </mergeCells>
   <conditionalFormatting sqref="Q159:Q163">
-    <cfRule type="containsText" dxfId="7" priority="5" operator="containsText" text="true">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="true">
       <formula>NOT(ISERROR(SEARCH("true",Q159)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="6" operator="containsText" text="false">
+    <cfRule type="containsText" dxfId="4" priority="6" operator="containsText" text="false">
       <formula>NOT(ISERROR(SEARCH("false",Q159)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R452:V701">
-    <cfRule type="containsText" dxfId="5" priority="3" operator="containsText" text="true">
-      <formula>NOT(ISERROR(SEARCH("true",R452)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="4" operator="containsText" text="false">
-      <formula>NOT(ISERROR(SEARCH("false",R452)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R451:V451">
+  <conditionalFormatting sqref="R451:V701">
     <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="true">
       <formula>NOT(ISERROR(SEARCH("true",R451)))</formula>
     </cfRule>
@@ -62951,36 +62874,36 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="17" t="s">
         <v>1340</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
     </row>
     <row r="3" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="12"/>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
+      <c r="A3" s="17"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
     </row>
     <row r="4" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="12"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
+      <c r="A4" s="17"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
@@ -63417,14 +63340,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="16" t="s">
         <v>1503</v>
       </c>
-      <c r="B1" s="13"/>
+      <c r="B1" s="16"/>
     </row>
     <row r="2" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="13"/>
-      <c r="B2" s="13"/>
+      <c r="A2" s="16"/>
+      <c r="B2" s="16"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
@@ -63973,14 +63896,14 @@
       </c>
     </row>
     <row r="29" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="13" t="s">
+      <c r="A29" s="16" t="s">
         <v>1504</v>
       </c>
-      <c r="B29" s="13"/>
+      <c r="B29" s="16"/>
     </row>
     <row r="30" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
-      <c r="B30" s="13"/>
+      <c r="A30" s="16"/>
+      <c r="B30" s="16"/>
     </row>
     <row r="31" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="32" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -64535,14 +64458,14 @@
     <row r="56" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="57" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="58" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="13" t="s">
+      <c r="A58" s="16" t="s">
         <v>1606</v>
       </c>
-      <c r="B58" s="13"/>
+      <c r="B58" s="16"/>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A59" s="13"/>
-      <c r="B59" s="13"/>
+      <c r="A59" s="16"/>
+      <c r="B59" s="16"/>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="6" t="s">
@@ -65169,7 +65092,7 @@
       <c r="G2" s="5" t="s">
         <v>1502</v>
       </c>
-      <c r="H2" s="16" t="s">
+      <c r="H2" s="5" t="s">
         <v>1565</v>
       </c>
       <c r="I2" s="3" t="s">
@@ -65198,7 +65121,7 @@
       <c r="G3" s="5" t="s">
         <v>1502</v>
       </c>
-      <c r="H3" s="16" t="s">
+      <c r="H3" s="5" t="s">
         <v>1565</v>
       </c>
       <c r="I3" s="3" t="s">
@@ -65227,10 +65150,10 @@
       <c r="G4" s="5" t="s">
         <v>1502</v>
       </c>
-      <c r="H4" s="16" t="s">
+      <c r="H4" s="5" t="s">
         <v>1566</v>
       </c>
-      <c r="I4" s="17" t="s">
+      <c r="I4" s="11" t="s">
         <v>1563</v>
       </c>
     </row>
@@ -65246,19 +65169,11 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G4">
-    <cfRule type="containsText" dxfId="25" priority="5" operator="containsText" text="FAIL">
-      <formula>NOT(ISERROR(SEARCH("FAIL",G4)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="24" priority="6" operator="containsText" text="PASS">
-      <formula>NOT(ISERROR(SEARCH("PASS",G4)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G3">
-    <cfRule type="containsText" dxfId="23" priority="3" operator="containsText" text="FAIL">
+  <conditionalFormatting sqref="G2:G4">
+    <cfRule type="containsText" dxfId="19" priority="3" operator="containsText" text="FAIL">
       <formula>NOT(ISERROR(SEARCH("FAIL",G2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="22" priority="4" operator="containsText" text="PASS">
+    <cfRule type="containsText" dxfId="18" priority="4" operator="containsText" text="PASS">
       <formula>NOT(ISERROR(SEARCH("PASS",G2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -65272,216 +65187,216 @@
   <dimension ref="A1:B26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.109375" style="19" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.77734375" style="19" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="8.88671875" style="19"/>
+    <col min="1" max="1" width="25.109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.77734375" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="8.88671875" style="13"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="12" t="s">
         <v>1655</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="12" t="s">
         <v>1607</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="14" t="s">
         <v>1656</v>
       </c>
-      <c r="B2" s="20">
+      <c r="B2" s="14">
         <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="14" t="s">
         <v>1657</v>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="14">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="14" t="s">
         <v>1658</v>
       </c>
-      <c r="B4" s="20">
+      <c r="B4" s="14">
         <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="14" t="s">
         <v>1659</v>
       </c>
-      <c r="B5" s="20">
+      <c r="B5" s="14">
         <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="14" t="s">
         <v>1660</v>
       </c>
-      <c r="B6" s="20">
+      <c r="B6" s="14">
         <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="14" t="s">
         <v>1661</v>
       </c>
-      <c r="B7" s="20">
+      <c r="B7" s="14">
         <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="14" t="s">
         <v>1662</v>
       </c>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="14" t="s">
         <v>1663</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="14" t="s">
         <v>1664</v>
       </c>
-      <c r="B9" s="20">
+      <c r="B9" s="14">
         <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="20" t="s">
+      <c r="A10" s="14" t="s">
         <v>1665</v>
       </c>
-      <c r="B10" s="20">
+      <c r="B10" s="14">
         <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="20" t="s">
+      <c r="A11" s="14" t="s">
         <v>1666</v>
       </c>
-      <c r="B11" s="20">
+      <c r="B11" s="14">
         <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="20" t="s">
+      <c r="A12" s="14" t="s">
         <v>1667</v>
       </c>
-      <c r="B12" s="20">
+      <c r="B12" s="14">
         <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="20" t="s">
+      <c r="A13" s="14" t="s">
         <v>1668</v>
       </c>
-      <c r="B13" s="20" t="s">
+      <c r="B13" s="14" t="s">
         <v>1565</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="20" t="s">
+      <c r="A14" s="14" t="s">
         <v>1669</v>
       </c>
-      <c r="B14" s="20">
+      <c r="B14" s="14">
         <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="20" t="s">
+      <c r="A15" s="14" t="s">
         <v>1670</v>
       </c>
-      <c r="B15" s="20">
+      <c r="B15" s="14">
         <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="20" t="s">
+      <c r="A16" s="14" t="s">
         <v>1671</v>
       </c>
-      <c r="B16" s="20">
+      <c r="B16" s="14">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="20" t="s">
+      <c r="A17" s="14" t="s">
         <v>1672</v>
       </c>
-      <c r="B17" s="20">
+      <c r="B17" s="14">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="20" t="s">
+      <c r="A18" s="14" t="s">
         <v>1673</v>
       </c>
-      <c r="B18" s="20" t="s">
+      <c r="B18" s="14" t="s">
         <v>1566</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="20" t="s">
+      <c r="A19" s="14" t="s">
         <v>1674</v>
       </c>
-      <c r="B19" s="20">
+      <c r="B19" s="14">
         <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="20" t="s">
+      <c r="A20" s="14" t="s">
         <v>1675</v>
       </c>
-      <c r="B20" s="20">
+      <c r="B20" s="14">
         <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="20" t="s">
+      <c r="A21" s="14" t="s">
         <v>1676</v>
       </c>
-      <c r="B21" s="20">
+      <c r="B21" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="20" t="s">
+      <c r="A22" s="14" t="s">
         <v>1677</v>
       </c>
-      <c r="B22" s="20">
+      <c r="B22" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="20" t="s">
+      <c r="A23" s="14" t="s">
         <v>1678</v>
       </c>
-      <c r="B23" s="20" t="s">
+      <c r="B23" s="14" t="s">
         <v>1679</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="20" t="s">
+      <c r="A24" s="14" t="s">
         <v>1680</v>
       </c>
-      <c r="B24" s="20">
+      <c r="B24" s="14">
         <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="20" t="s">
+      <c r="A25" s="14" t="s">
         <v>1681</v>
       </c>
-      <c r="B25" s="20">
+      <c r="B25" s="14">
         <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="20" t="s">
+      <c r="A26" s="14" t="s">
         <v>1682</v>
       </c>
-      <c r="B26" s="20">
+      <c r="B26" s="14">
         <v>1</v>
       </c>
     </row>

--- a/PEI_requirements.xlsx
+++ b/PEI_requirements.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB71CA0E-D03F-48B1-B7F1-7EB7DEDA7F57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="5" activeTab="9" xr2:uid="{BF88EDFC-CE2B-40C6-8F71-DF8E3BFC082E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{BF88EDFC-CE2B-40C6-8F71-DF8E3BFC082E}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet index - content" sheetId="20" r:id="rId1"/>
